--- a/Employee-20260901200132.xlsx.xlsx
+++ b/Employee-20260901200132.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359F4271-8B50-4267-B56D-946341067D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D98329-75D7-412B-9C0E-546B08622742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="0" windowWidth="13935" windowHeight="14655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="人事資料" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="963">
   <si>
     <t>員工編號</t>
   </si>
@@ -815,9 +815,6 @@
   </si>
   <si>
     <t>CRM高專PLUS</t>
-  </si>
-  <si>
-    <t>新加坡</t>
   </si>
   <si>
     <t>KMH00852</t>
@@ -2908,6 +2905,18 @@
   </si>
   <si>
     <t>所屬院所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>博愛院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>開元院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信義院</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2916,7 +2925,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
+    <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -2974,7 +2983,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2984,7 +2993,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3320,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -4676,7 +4685,7 @@
         <v>132</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D98" s="5">
         <v>46217</v>
@@ -4746,7 +4755,7 @@
         <v>132</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D103" s="5">
         <v>46175</v>
@@ -5054,7 +5063,7 @@
         <v>163</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D125" s="5">
         <v>46360</v>
@@ -6356,7 +6365,7 @@
         <v>261</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D218" s="5">
         <v>46356</v>
@@ -6370,7 +6379,7 @@
         <v>263</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>264</v>
+        <v>960</v>
       </c>
       <c r="D219" s="5">
         <v>46179</v>
@@ -6378,7 +6387,7 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>9</v>
@@ -6392,7 +6401,7 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>9</v>
@@ -6406,7 +6415,7 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>5</v>
@@ -6420,7 +6429,7 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>9</v>
@@ -6434,7 +6443,7 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>97</v>
@@ -6448,7 +6457,7 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>20</v>
@@ -6462,7 +6471,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>20</v>
@@ -6476,7 +6485,7 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>20</v>
@@ -6490,7 +6499,7 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>20</v>
@@ -6504,7 +6513,7 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>20</v>
@@ -6518,7 +6527,7 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>20</v>
@@ -6532,10 +6541,10 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>250</v>
@@ -6546,7 +6555,7 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>20</v>
@@ -6560,7 +6569,7 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>20</v>
@@ -6574,7 +6583,7 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>22</v>
@@ -6588,7 +6597,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>20</v>
@@ -6602,7 +6611,7 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>20</v>
@@ -6616,7 +6625,7 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>22</v>
@@ -6630,7 +6639,7 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>9</v>
@@ -6644,7 +6653,7 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>9</v>
@@ -6658,13 +6667,13 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C240" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="D240" s="5">
         <v>46142</v>
@@ -6672,7 +6681,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>22</v>
@@ -6686,7 +6695,7 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>9</v>
@@ -6700,7 +6709,7 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>22</v>
@@ -6714,7 +6723,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>20</v>
@@ -6728,7 +6737,7 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>150</v>
@@ -6742,7 +6751,7 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>22</v>
@@ -6756,7 +6765,7 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>9</v>
@@ -6770,7 +6779,7 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>48</v>
@@ -6784,7 +6793,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>48</v>
@@ -6798,7 +6807,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>48</v>
@@ -6812,7 +6821,7 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>20</v>
@@ -6826,13 +6835,13 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C252" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="D252" s="5">
         <v>46044</v>
@@ -6840,13 +6849,13 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D253" s="5">
         <v>46054</v>
@@ -6854,13 +6863,13 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D254" s="5">
         <v>46073</v>
@@ -6868,13 +6877,13 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="D255" s="5">
         <v>46281</v>
@@ -6882,7 +6891,7 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>81</v>
@@ -6896,13 +6905,13 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D257" s="5">
         <v>46145</v>
@@ -6910,13 +6919,13 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D258" s="5">
         <v>46252</v>
@@ -6924,13 +6933,13 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D259" s="5">
         <v>46300</v>
@@ -6938,10 +6947,10 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B260" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>6</v>
@@ -6952,13 +6961,13 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D261" s="5">
         <v>46146</v>
@@ -6966,13 +6975,13 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D262" s="5">
         <v>46195</v>
@@ -6980,13 +6989,13 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D263" s="5">
         <v>46190</v>
@@ -6994,13 +7003,13 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D264" s="5">
         <v>46217</v>
@@ -7008,13 +7017,13 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D265" s="5">
         <v>46135</v>
@@ -7022,13 +7031,13 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D266" s="5">
         <v>46137</v>
@@ -7036,13 +7045,13 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D267" s="5">
         <v>46224</v>
@@ -7050,13 +7059,13 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D268" s="5">
         <v>46054</v>
@@ -7064,13 +7073,13 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D269" s="5">
         <v>46356</v>
@@ -7078,13 +7087,13 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D270" s="5">
         <v>46236</v>
@@ -7092,13 +7101,13 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D271" s="5">
         <v>46072</v>
@@ -7106,13 +7115,13 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D272" s="5">
         <v>46090</v>
@@ -7120,13 +7129,13 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="D273" s="5">
         <v>46186</v>
@@ -7134,7 +7143,7 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>9</v>
@@ -7148,7 +7157,7 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>31</v>
@@ -7162,7 +7171,7 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>92</v>
@@ -7176,7 +7185,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>22</v>
@@ -7190,7 +7199,7 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>16</v>
@@ -7204,13 +7213,13 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D279" s="5">
         <v>46319</v>
@@ -7218,7 +7227,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>22</v>
@@ -7232,13 +7241,13 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D281" s="5">
         <v>46308</v>
@@ -7246,7 +7255,7 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>198</v>
@@ -7260,13 +7269,13 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D283" s="5">
         <v>46322</v>
@@ -7274,13 +7283,13 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D284" s="5">
         <v>46114</v>
@@ -7288,10 +7297,10 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>6</v>
@@ -7302,13 +7311,13 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D286" s="5">
         <v>46030</v>
@@ -7316,7 +7325,7 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>22</v>
@@ -7330,7 +7339,7 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>9</v>
@@ -7344,7 +7353,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>263</v>
@@ -7358,13 +7367,13 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D290" s="5">
         <v>46104</v>
@@ -7372,7 +7381,7 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>81</v>
@@ -7386,13 +7395,13 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D292" s="5">
         <v>46387</v>
@@ -7400,13 +7409,13 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D293" s="5">
         <v>46279</v>
@@ -7414,13 +7423,13 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D294" s="5">
         <v>46045</v>
@@ -7428,13 +7437,13 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D295" s="5">
         <v>46206</v>
@@ -7442,13 +7451,13 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D296" s="5">
         <v>46193</v>
@@ -7456,13 +7465,13 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D297" s="5">
         <v>46323</v>
@@ -7470,13 +7479,13 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D298" s="5">
         <v>46084</v>
@@ -7484,13 +7493,13 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D299" s="5">
         <v>46224</v>
@@ -7498,13 +7507,13 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D300" s="5">
         <v>46361</v>
@@ -7512,7 +7521,7 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>150</v>
@@ -7526,13 +7535,13 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D302" s="5">
         <v>46264</v>
@@ -7540,13 +7549,13 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D303" s="5">
         <v>46383</v>
@@ -7554,13 +7563,13 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D304" s="5">
         <v>46267</v>
@@ -7568,13 +7577,13 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D305" s="5">
         <v>46222</v>
@@ -7582,13 +7591,13 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D306" s="5">
         <v>46287</v>
@@ -7596,13 +7605,13 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D307" s="5">
         <v>46077</v>
@@ -7610,13 +7619,13 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D308" s="5">
         <v>46215</v>
@@ -7624,13 +7633,13 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D309" s="5">
         <v>46105</v>
@@ -7638,13 +7647,13 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D310" s="5">
         <v>46318</v>
@@ -7652,13 +7661,13 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D311" s="5">
         <v>46229</v>
@@ -7666,7 +7675,7 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>9</v>
@@ -7680,7 +7689,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>22</v>
@@ -7694,7 +7703,7 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>81</v>
@@ -7708,7 +7717,7 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>5</v>
@@ -7722,7 +7731,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>20</v>
@@ -7736,7 +7745,7 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>31</v>
@@ -7750,7 +7759,7 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>31</v>
@@ -7764,7 +7773,7 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>9</v>
@@ -7778,7 +7787,7 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>20</v>
@@ -7792,7 +7801,7 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>20</v>
@@ -7806,13 +7815,13 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D322" s="5">
         <v>46294</v>
@@ -7820,7 +7829,7 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>92</v>
@@ -7834,7 +7843,7 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>81</v>
@@ -7848,7 +7857,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>9</v>
@@ -7862,7 +7871,7 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>97</v>
@@ -7876,7 +7885,7 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>9</v>
@@ -7890,7 +7899,7 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>22</v>
@@ -7904,7 +7913,7 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>9</v>
@@ -7918,7 +7927,7 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>20</v>
@@ -7932,7 +7941,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>198</v>
@@ -7946,7 +7955,7 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>20</v>
@@ -7960,7 +7969,7 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>22</v>
@@ -7974,7 +7983,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>81</v>
@@ -7988,7 +7997,7 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>22</v>
@@ -8002,7 +8011,7 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>22</v>
@@ -8016,7 +8025,7 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>20</v>
@@ -8030,7 +8039,7 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>27</v>
@@ -8044,7 +8053,7 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>5</v>
@@ -8058,7 +8067,7 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>9</v>
@@ -8072,7 +8081,7 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>9</v>
@@ -8086,7 +8095,7 @@
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>22</v>
@@ -8100,7 +8109,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>20</v>
@@ -8114,7 +8123,7 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>9</v>
@@ -8128,7 +8137,7 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>9</v>
@@ -8142,7 +8151,7 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>20</v>
@@ -8156,7 +8165,7 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>22</v>
@@ -8170,7 +8179,7 @@
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>20</v>
@@ -8184,7 +8193,7 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>9</v>
@@ -8198,7 +8207,7 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>48</v>
@@ -8212,7 +8221,7 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>9</v>
@@ -8226,7 +8235,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>81</v>
@@ -8240,7 +8249,7 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>22</v>
@@ -8254,7 +8263,7 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>9</v>
@@ -8268,7 +8277,7 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>9</v>
@@ -8282,7 +8291,7 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>9</v>
@@ -8296,10 +8305,10 @@
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>82</v>
@@ -8310,7 +8319,7 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>97</v>
@@ -8324,7 +8333,7 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>20</v>
@@ -8338,13 +8347,13 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D360" s="5">
         <v>46192</v>
@@ -8352,7 +8361,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>20</v>
@@ -8366,7 +8375,7 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>97</v>
@@ -8380,7 +8389,7 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>20</v>
@@ -8394,7 +8403,7 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>22</v>
@@ -8408,7 +8417,7 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>20</v>
@@ -8422,7 +8431,7 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>22</v>
@@ -8436,7 +8445,7 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>20</v>
@@ -8450,7 +8459,7 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>22</v>
@@ -8464,7 +8473,7 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>9</v>
@@ -8478,7 +8487,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>22</v>
@@ -8492,7 +8501,7 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>9</v>
@@ -8506,7 +8515,7 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>9</v>
@@ -8520,7 +8529,7 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>20</v>
@@ -8534,7 +8543,7 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>20</v>
@@ -8548,7 +8557,7 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>5</v>
@@ -8562,7 +8571,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>22</v>
@@ -8576,7 +8585,7 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>27</v>
@@ -8590,7 +8599,7 @@
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>22</v>
@@ -8604,7 +8613,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>22</v>
@@ -8618,7 +8627,7 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>20</v>
@@ -8632,13 +8641,13 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D381" s="5">
         <v>46051</v>
@@ -8646,7 +8655,7 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>22</v>
@@ -8660,13 +8669,13 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D383" s="5">
         <v>46034</v>
@@ -8674,13 +8683,13 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D384" s="5">
         <v>46199</v>
@@ -8688,13 +8697,13 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D385" s="5">
         <v>46162</v>
@@ -8702,7 +8711,7 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>92</v>
@@ -8716,7 +8725,7 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>9</v>
@@ -8730,7 +8739,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>150</v>
@@ -8744,13 +8753,13 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D389" s="5">
         <v>46168</v>
@@ -8758,13 +8767,13 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D390" s="5">
         <v>46382</v>
@@ -8772,13 +8781,13 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D391" s="5">
         <v>46271</v>
@@ -8786,13 +8795,13 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D392" s="5">
         <v>46295</v>
@@ -8800,13 +8809,13 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D393" s="5">
         <v>46067</v>
@@ -8814,7 +8823,7 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>22</v>
@@ -8828,13 +8837,13 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D395" s="5">
         <v>46068</v>
@@ -8842,13 +8851,13 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D396" s="5">
         <v>46277</v>
@@ -8856,13 +8865,13 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D397" s="5">
         <v>46288</v>
@@ -8870,13 +8879,13 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D398" s="5">
         <v>46114</v>
@@ -8884,13 +8893,13 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D399" s="5">
         <v>46174</v>
@@ -8898,13 +8907,13 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D400" s="5">
         <v>46098</v>
@@ -8912,13 +8921,13 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D401" s="5">
         <v>46043</v>
@@ -8926,13 +8935,13 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D402" s="5">
         <v>46081</v>
@@ -8940,13 +8949,13 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D403" s="5">
         <v>46085</v>
@@ -8954,13 +8963,13 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D404" s="5">
         <v>46213</v>
@@ -8968,13 +8977,13 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D405" s="5">
         <v>46044</v>
@@ -8982,13 +8991,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D406" s="5">
         <v>46026</v>
@@ -8996,7 +9005,7 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>20</v>
@@ -9010,13 +9019,13 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D408" s="5">
         <v>46034</v>
@@ -9024,13 +9033,13 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D409" s="5">
         <v>46250</v>
@@ -9038,13 +9047,13 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D410" s="5">
         <v>46179</v>
@@ -9052,7 +9061,7 @@
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>20</v>
@@ -9066,7 +9075,7 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>22</v>
@@ -9080,7 +9089,7 @@
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>9</v>
@@ -9094,7 +9103,7 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>9</v>
@@ -9108,7 +9117,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>9</v>
@@ -9122,7 +9131,7 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>20</v>
@@ -9136,7 +9145,7 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>22</v>
@@ -9150,7 +9159,7 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>20</v>
@@ -9164,7 +9173,7 @@
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>20</v>
@@ -9178,7 +9187,7 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>22</v>
@@ -9192,7 +9201,7 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>20</v>
@@ -9206,7 +9215,7 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>22</v>
@@ -9220,7 +9229,7 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>9</v>
@@ -9234,7 +9243,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>22</v>
@@ -9248,7 +9257,7 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>22</v>
@@ -9262,7 +9271,7 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>9</v>
@@ -9276,7 +9285,7 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>22</v>
@@ -9290,7 +9299,7 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>150</v>
@@ -9304,7 +9313,7 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>20</v>
@@ -9318,7 +9327,7 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>27</v>
@@ -9332,7 +9341,7 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>20</v>
@@ -9346,7 +9355,7 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>20</v>
@@ -9360,7 +9369,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>20</v>
@@ -9374,7 +9383,7 @@
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>20</v>
@@ -9388,7 +9397,7 @@
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>22</v>
@@ -9402,7 +9411,7 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>22</v>
@@ -9416,7 +9425,7 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>87</v>
@@ -9430,7 +9439,7 @@
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>20</v>
@@ -9444,7 +9453,7 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>9</v>
@@ -9458,7 +9467,7 @@
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>20</v>
@@ -9472,7 +9481,7 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>22</v>
@@ -9486,7 +9495,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>20</v>
@@ -9500,7 +9509,7 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>27</v>
@@ -9514,7 +9523,7 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>20</v>
@@ -9528,7 +9537,7 @@
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>20</v>
@@ -9542,7 +9551,7 @@
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>20</v>
@@ -9556,7 +9565,7 @@
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>20</v>
@@ -9570,7 +9579,7 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>48</v>
@@ -9584,7 +9593,7 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>48</v>
@@ -9598,10 +9607,10 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B450" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="B450" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>57</v>
@@ -9612,7 +9621,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>48</v>
@@ -9624,7 +9633,7 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>14</v>
@@ -9638,7 +9647,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>128</v>
@@ -9652,10 +9661,10 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B454" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="B454" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>6</v>
@@ -9666,7 +9675,7 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>16</v>
@@ -9680,10 +9689,10 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B456" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="B456" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>6</v>
@@ -9694,7 +9703,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>3</v>
@@ -9708,10 +9717,10 @@
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B458" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="B458" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>6</v>
@@ -9722,10 +9731,10 @@
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B459" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="B459" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>6</v>
@@ -9736,10 +9745,10 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B460" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="B460" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>6</v>
@@ -9750,7 +9759,7 @@
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>198</v>
@@ -9764,10 +9773,10 @@
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B462" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="B462" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>6</v>
@@ -9778,10 +9787,10 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B463" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="B463" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>6</v>
@@ -9792,7 +9801,7 @@
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>128</v>
@@ -9806,7 +9815,7 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>128</v>
@@ -9820,10 +9829,10 @@
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B466" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="B466" s="2" t="s">
-        <v>530</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>6</v>
@@ -9834,7 +9843,7 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>128</v>
@@ -9848,7 +9857,7 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>3</v>
@@ -9862,7 +9871,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>132</v>
@@ -9876,7 +9885,7 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>3</v>
@@ -9890,7 +9899,7 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>132</v>
@@ -9904,10 +9913,10 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B472" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="B472" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>6</v>
@@ -9918,7 +9927,7 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>4</v>
@@ -9932,7 +9941,7 @@
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>198</v>
@@ -9946,7 +9955,7 @@
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>132</v>
@@ -9960,10 +9969,10 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B476" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="B476" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>6</v>
@@ -9974,7 +9983,7 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>3</v>
@@ -9988,7 +9997,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>132</v>
@@ -10002,7 +10011,7 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>4</v>
@@ -10016,7 +10025,7 @@
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>198</v>
@@ -10030,7 +10039,7 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>198</v>
@@ -10044,7 +10053,7 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>3</v>
@@ -10058,10 +10067,10 @@
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B483" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="B483" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>6</v>
@@ -10072,10 +10081,10 @@
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B484" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="B484" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>6</v>
@@ -10086,10 +10095,10 @@
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>6</v>
@@ -10100,13 +10109,13 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>264</v>
+        <v>961</v>
       </c>
       <c r="D486" s="5">
         <v>46023</v>
@@ -10114,13 +10123,13 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C487" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="B487" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C487" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="D487" s="5">
         <v>46225</v>
@@ -10128,7 +10137,7 @@
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>9</v>
@@ -10142,13 +10151,13 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D489" s="5">
         <v>46179</v>
@@ -10156,13 +10165,13 @@
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D490" s="5">
         <v>46038</v>
@@ -10170,13 +10179,13 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B491" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="B491" s="2" t="s">
-        <v>561</v>
-      </c>
       <c r="C491" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D491" s="5">
         <v>46071</v>
@@ -10184,13 +10193,13 @@
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D492" s="5">
         <v>46368</v>
@@ -10198,13 +10207,13 @@
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C493" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="B493" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C493" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="D493" s="5">
         <v>46346</v>
@@ -10212,13 +10221,13 @@
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D494" s="5">
         <v>46025</v>
@@ -10226,13 +10235,13 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D495" s="5">
         <v>46372</v>
@@ -10240,13 +10249,13 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D496" s="5">
         <v>46321</v>
@@ -10254,13 +10263,13 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D497" s="5">
         <v>46042</v>
@@ -10268,13 +10277,13 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D498" s="5">
         <v>46122</v>
@@ -10282,13 +10291,13 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D499" s="5">
         <v>46230</v>
@@ -10296,13 +10305,13 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D500" s="5">
         <v>46338</v>
@@ -10310,13 +10319,13 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D501" s="5">
         <v>46063</v>
@@ -10324,13 +10333,13 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D502" s="5">
         <v>46057</v>
@@ -10338,13 +10347,13 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D503" s="5">
         <v>46032</v>
@@ -10352,13 +10361,13 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D504" s="5">
         <v>46311</v>
@@ -10366,13 +10375,13 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D505" s="5">
         <v>46329</v>
@@ -10380,13 +10389,13 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D506" s="5">
         <v>46322</v>
@@ -10394,13 +10403,13 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D507" s="5">
         <v>46166</v>
@@ -10408,13 +10417,13 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D508" s="5">
         <v>46151</v>
@@ -10422,7 +10431,7 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>22</v>
@@ -10436,13 +10445,13 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D510" s="5">
         <v>46283</v>
@@ -10450,13 +10459,13 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D511" s="5">
         <v>46312</v>
@@ -10464,13 +10473,13 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D512" s="5">
         <v>46096</v>
@@ -10478,13 +10487,13 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D513" s="5">
         <v>46361</v>
@@ -10492,13 +10501,13 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D514" s="5">
         <v>46247</v>
@@ -10506,13 +10515,13 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D515" s="5">
         <v>46130</v>
@@ -10520,13 +10529,13 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D516" s="5">
         <v>46078</v>
@@ -10534,13 +10543,13 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D517" s="5">
         <v>46131</v>
@@ -10548,13 +10557,13 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D518" s="5">
         <v>46362</v>
@@ -10562,13 +10571,13 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B519" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B519" s="2" t="s">
-        <v>592</v>
-      </c>
       <c r="C519" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D519" s="5">
         <v>46169</v>
@@ -10576,13 +10585,13 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D520" s="5">
         <v>46279</v>
@@ -10590,13 +10599,13 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D521" s="5">
         <v>46113</v>
@@ -10604,7 +10613,7 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>31</v>
@@ -10618,13 +10627,13 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C523" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="B523" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C523" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="D523" s="5">
         <v>46258</v>
@@ -10632,13 +10641,13 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>264</v>
+        <v>961</v>
       </c>
       <c r="D524" s="5">
         <v>46180</v>
@@ -10646,13 +10655,13 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D525" s="5">
         <v>46114</v>
@@ -10660,7 +10669,7 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>20</v>
@@ -10674,13 +10683,13 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B527" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="B527" s="2" t="s">
-        <v>602</v>
-      </c>
       <c r="C527" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D527" s="5">
         <v>46342</v>
@@ -10688,7 +10697,7 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>81</v>
@@ -10702,7 +10711,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>150</v>
@@ -10716,13 +10725,13 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D530" s="5">
         <v>46337</v>
@@ -10730,13 +10739,13 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D531" s="5">
         <v>46287</v>
@@ -10744,13 +10753,13 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D532" s="5">
         <v>46087</v>
@@ -10758,13 +10767,13 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D533" s="5">
         <v>46218</v>
@@ -10772,13 +10781,13 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D534" s="5">
         <v>46351</v>
@@ -10786,13 +10795,13 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D535" s="5">
         <v>46267</v>
@@ -10800,13 +10809,13 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D536" s="5">
         <v>46198</v>
@@ -10814,7 +10823,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>22</v>
@@ -10828,13 +10837,13 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D538" s="5">
         <v>46088</v>
@@ -10842,13 +10851,13 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D539" s="5">
         <v>46052</v>
@@ -10856,13 +10865,13 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D540" s="5">
         <v>46104</v>
@@ -10870,13 +10879,13 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D541" s="5">
         <v>46091</v>
@@ -10884,13 +10893,13 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D542" s="5">
         <v>46197</v>
@@ -10898,13 +10907,13 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D543" s="5">
         <v>46029</v>
@@ -10912,13 +10921,13 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D544" s="5">
         <v>46353</v>
@@ -10926,13 +10935,13 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D545" s="5">
         <v>46358</v>
@@ -10940,13 +10949,13 @@
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D546" s="5">
         <v>46386</v>
@@ -10954,13 +10963,13 @@
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D547" s="5">
         <v>46334</v>
@@ -10968,13 +10977,13 @@
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D548" s="5">
         <v>46288</v>
@@ -10982,7 +10991,7 @@
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>9</v>
@@ -10996,13 +11005,13 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D550" s="5">
         <v>46186</v>
@@ -11010,13 +11019,13 @@
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D551" s="5">
         <v>46232</v>
@@ -11024,13 +11033,13 @@
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D552" s="5">
         <v>46255</v>
@@ -11038,13 +11047,13 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D553" s="5">
         <v>46296</v>
@@ -11052,13 +11061,13 @@
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D554" s="5">
         <v>46139</v>
@@ -11066,13 +11075,13 @@
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D555" s="5">
         <v>46081</v>
@@ -11080,13 +11089,13 @@
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D556" s="5">
         <v>46079</v>
@@ -11094,13 +11103,13 @@
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D557" s="5">
         <v>46282</v>
@@ -11108,13 +11117,13 @@
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D558" s="5">
         <v>46183</v>
@@ -11122,13 +11131,13 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D559" s="5">
         <v>46304</v>
@@ -11136,13 +11145,13 @@
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D560" s="5">
         <v>46087</v>
@@ -11150,13 +11159,13 @@
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D561" s="5">
         <v>46117</v>
@@ -11164,13 +11173,13 @@
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D562" s="5">
         <v>46174</v>
@@ -11178,13 +11187,13 @@
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D563" s="5">
         <v>46245</v>
@@ -11192,13 +11201,13 @@
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D564" s="5">
         <v>46110</v>
@@ -11206,13 +11215,13 @@
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D565" s="5">
         <v>46379</v>
@@ -11220,13 +11229,13 @@
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D566" s="5">
         <v>46291</v>
@@ -11234,13 +11243,13 @@
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D567" s="5">
         <v>46226</v>
@@ -11248,13 +11257,13 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D568" s="5">
         <v>46100</v>
@@ -11262,13 +11271,13 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D569" s="5">
         <v>46329</v>
@@ -11276,13 +11285,13 @@
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D570" s="5">
         <v>46030</v>
@@ -11290,13 +11299,13 @@
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D571" s="5">
         <v>46373</v>
@@ -11304,7 +11313,7 @@
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>97</v>
@@ -11318,7 +11327,7 @@
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>20</v>
@@ -11332,13 +11341,13 @@
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D574" s="5">
         <v>46145</v>
@@ -11346,7 +11355,7 @@
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>5</v>
@@ -11360,7 +11369,7 @@
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>20</v>
@@ -11374,13 +11383,13 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D577" s="5">
         <v>46031</v>
@@ -11388,13 +11397,13 @@
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D578" s="5">
         <v>46033</v>
@@ -11402,7 +11411,7 @@
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>20</v>
@@ -11416,7 +11425,7 @@
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>92</v>
@@ -11430,7 +11439,7 @@
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>20</v>
@@ -11444,13 +11453,13 @@
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D582" s="5">
         <v>46048</v>
@@ -11458,7 +11467,7 @@
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>20</v>
@@ -11472,7 +11481,7 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>9</v>
@@ -11486,13 +11495,13 @@
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D585" s="5">
         <v>46034</v>
@@ -11500,7 +11509,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>20</v>
@@ -11514,13 +11523,13 @@
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D587" s="5">
         <v>46203</v>
@@ -11528,7 +11537,7 @@
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>9</v>
@@ -11542,7 +11551,7 @@
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>9</v>
@@ -11556,7 +11565,7 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>87</v>
@@ -11570,13 +11579,13 @@
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>263</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D591" s="5">
         <v>46034</v>
@@ -11584,7 +11593,7 @@
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>22</v>
@@ -11598,13 +11607,13 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D593" s="5">
         <v>46217</v>
@@ -11612,7 +11621,7 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>20</v>
@@ -11626,7 +11635,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>9</v>
@@ -11640,7 +11649,7 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>5</v>
@@ -11654,7 +11663,7 @@
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>20</v>
@@ -11668,7 +11677,7 @@
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>20</v>
@@ -11682,7 +11691,7 @@
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>20</v>
@@ -11696,7 +11705,7 @@
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>20</v>
@@ -11710,7 +11719,7 @@
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>22</v>
@@ -11724,7 +11733,7 @@
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>22</v>
@@ -11738,7 +11747,7 @@
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>9</v>
@@ -11752,13 +11761,13 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D604" s="5">
         <v>46037</v>
@@ -11766,13 +11775,13 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D605" s="5">
         <v>46247</v>
@@ -11780,7 +11789,7 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>22</v>
@@ -11794,7 +11803,7 @@
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>22</v>
@@ -11808,7 +11817,7 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>46</v>
@@ -11822,7 +11831,7 @@
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>48</v>
@@ -11836,7 +11845,7 @@
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>9</v>
@@ -11850,13 +11859,13 @@
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D611" s="5">
         <v>46165</v>
@@ -11864,13 +11873,13 @@
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D612" s="5">
         <v>46249</v>
@@ -11878,13 +11887,13 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D613" s="5">
         <v>46227</v>
@@ -11892,13 +11901,13 @@
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D614" s="5">
         <v>46145</v>
@@ -11906,13 +11915,13 @@
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D615" s="5">
         <v>46200</v>
@@ -11920,13 +11929,13 @@
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D616" s="5">
         <v>46292</v>
@@ -11934,13 +11943,13 @@
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D617" s="5">
         <v>46290</v>
@@ -11948,13 +11957,13 @@
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D618" s="5">
         <v>46197</v>
@@ -11962,13 +11971,13 @@
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D619" s="5">
         <v>46301</v>
@@ -11976,13 +11985,13 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C620" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D620" s="5">
         <v>46048</v>
@@ -11990,13 +11999,13 @@
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C621" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D621" s="5">
         <v>46365</v>
@@ -12004,13 +12013,13 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D622" s="5">
         <v>46136</v>
@@ -12018,13 +12027,13 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D623" s="5">
         <v>46333</v>
@@ -12032,13 +12041,13 @@
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C624" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D624" s="5">
         <v>46201</v>
@@ -12046,13 +12055,13 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D625" s="5">
         <v>46274</v>
@@ -12060,13 +12069,13 @@
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C626" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D626" s="5">
         <v>46376</v>
@@ -12074,13 +12083,13 @@
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B627" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="B627" s="2" t="s">
-        <v>703</v>
-      </c>
       <c r="C627" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D627" s="5">
         <v>46130</v>
@@ -12088,13 +12097,13 @@
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D628" s="5">
         <v>46220</v>
@@ -12102,13 +12111,13 @@
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D629" s="5">
         <v>46348</v>
@@ -12116,13 +12125,13 @@
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C630" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="B630" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C630" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="D630" s="5">
         <v>46368</v>
@@ -12130,13 +12139,13 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D631" s="5">
         <v>46252</v>
@@ -12144,13 +12153,13 @@
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D632" s="5">
         <v>46282</v>
@@ -12158,13 +12167,13 @@
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D633" s="5">
         <v>46052</v>
@@ -12172,13 +12181,13 @@
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D634" s="5">
         <v>46032</v>
@@ -12186,13 +12195,13 @@
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D635" s="5">
         <v>46387</v>
@@ -12200,13 +12209,13 @@
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D636" s="5">
         <v>46358</v>
@@ -12214,13 +12223,13 @@
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D637" s="5">
         <v>46063</v>
@@ -12228,13 +12237,13 @@
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D638" s="5">
         <v>46063</v>
@@ -12242,13 +12251,13 @@
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D639" s="5">
         <v>46107</v>
@@ -12256,13 +12265,13 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D640" s="5">
         <v>46374</v>
@@ -12270,13 +12279,13 @@
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D641" s="5">
         <v>46131</v>
@@ -12284,13 +12293,13 @@
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D642" s="5">
         <v>46124</v>
@@ -12298,13 +12307,13 @@
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D643" s="5">
         <v>46118</v>
@@ -12312,13 +12321,13 @@
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B644" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D644" s="5">
         <v>46023</v>
@@ -12326,13 +12335,13 @@
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B645" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D645" s="5">
         <v>46227</v>
@@ -12340,13 +12349,13 @@
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B646" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D646" s="5">
         <v>46268</v>
@@ -12354,13 +12363,13 @@
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B647" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D647" s="5">
         <v>46180</v>
@@ -12368,13 +12377,13 @@
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B648" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D648" s="5">
         <v>46336</v>
@@ -12382,13 +12391,13 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D649" s="5">
         <v>46320</v>
@@ -12396,13 +12405,13 @@
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B650" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D650" s="5">
         <v>46173</v>
@@ -12410,13 +12419,13 @@
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B651" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D651" s="5">
         <v>46387</v>
@@ -12424,13 +12433,13 @@
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D652" s="5">
         <v>46336</v>
@@ -12438,13 +12447,13 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D653" s="5">
         <v>46201</v>
@@ -12452,7 +12461,7 @@
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>22</v>
@@ -12466,13 +12475,13 @@
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D655" s="5">
         <v>46064</v>
@@ -12480,13 +12489,13 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C656" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D656" s="5">
         <v>46183</v>
@@ -12494,13 +12503,13 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C657" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D657" s="5">
         <v>46157</v>
@@ -12508,13 +12517,13 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D658" s="5">
         <v>46314</v>
@@ -12522,13 +12531,13 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D659" s="5">
         <v>46242</v>
@@ -12536,13 +12545,13 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C660" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D660" s="5">
         <v>46270</v>
@@ -12550,13 +12559,13 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D661" s="5">
         <v>46023</v>
@@ -12564,13 +12573,13 @@
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D662" s="5">
         <v>46378</v>
@@ -12578,13 +12587,13 @@
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D663" s="5">
         <v>46344</v>
@@ -12592,13 +12601,13 @@
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D664" s="5">
         <v>46182</v>
@@ -12606,13 +12615,13 @@
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D665" s="5">
         <v>46290</v>
@@ -12620,13 +12629,13 @@
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D666" s="5">
         <v>46201</v>
@@ -12634,13 +12643,13 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D667" s="5">
         <v>46303</v>
@@ -12648,7 +12657,7 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>22</v>
@@ -12662,7 +12671,7 @@
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>31</v>
@@ -12676,7 +12685,7 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>20</v>
@@ -12690,7 +12699,7 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>9</v>
@@ -12704,7 +12713,7 @@
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>97</v>
@@ -12718,7 +12727,7 @@
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>20</v>
@@ -12732,7 +12741,7 @@
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>150</v>
@@ -12746,7 +12755,7 @@
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>9</v>
@@ -12760,7 +12769,7 @@
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B676" s="2" t="s">
         <v>20</v>
@@ -12774,7 +12783,7 @@
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B677" s="2" t="s">
         <v>22</v>
@@ -12788,7 +12797,7 @@
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B678" s="2" t="s">
         <v>20</v>
@@ -12802,7 +12811,7 @@
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>20</v>
@@ -12816,7 +12825,7 @@
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B680" s="2" t="s">
         <v>20</v>
@@ -12830,7 +12839,7 @@
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>97</v>
@@ -12844,7 +12853,7 @@
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B682" s="2" t="s">
         <v>22</v>
@@ -12858,7 +12867,7 @@
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>20</v>
@@ -12872,7 +12881,7 @@
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>120</v>
@@ -12886,7 +12895,7 @@
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>46</v>
@@ -12900,7 +12909,7 @@
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B686" s="2" t="s">
         <v>20</v>
@@ -12914,7 +12923,7 @@
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>9</v>
@@ -12928,7 +12937,7 @@
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>9</v>
@@ -12942,7 +12951,7 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B689" s="2" t="s">
         <v>20</v>
@@ -12956,7 +12965,7 @@
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>22</v>
@@ -12970,7 +12979,7 @@
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B691" s="2" t="s">
         <v>20</v>
@@ -12984,7 +12993,7 @@
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B692" s="2" t="s">
         <v>22</v>
@@ -12998,7 +13007,7 @@
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>22</v>
@@ -13012,7 +13021,7 @@
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B694" s="2" t="s">
         <v>9</v>
@@ -13026,7 +13035,7 @@
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B695" s="2" t="s">
         <v>22</v>
@@ -13040,7 +13049,7 @@
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B696" s="2" t="s">
         <v>46</v>
@@ -13054,10 +13063,10 @@
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C697" s="2" t="s">
         <v>184</v>
@@ -13068,13 +13077,13 @@
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B698" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D698" s="5">
         <v>46370</v>
@@ -13082,13 +13091,13 @@
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B699" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D699" s="5">
         <v>46323</v>
@@ -13096,13 +13105,13 @@
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B700" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D700" s="5">
         <v>46353</v>
@@ -13110,13 +13119,13 @@
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B701" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D701" s="5">
         <v>46356</v>
@@ -13124,13 +13133,13 @@
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B702" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D702" s="5">
         <v>46297</v>
@@ -13138,13 +13147,13 @@
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B703" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D703" s="5">
         <v>46321</v>
@@ -13152,13 +13161,13 @@
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B704" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D704" s="5">
         <v>46158</v>
@@ -13166,13 +13175,13 @@
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B705" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D705" s="5">
         <v>46077</v>
@@ -13180,13 +13189,13 @@
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B706" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D706" s="5">
         <v>46329</v>
@@ -13194,13 +13203,13 @@
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B707" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D707" s="5">
         <v>46185</v>
@@ -13208,7 +13217,7 @@
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B708" s="2" t="s">
         <v>3</v>
@@ -13222,13 +13231,13 @@
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B709" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D709" s="5">
         <v>46125</v>
@@ -13236,13 +13245,13 @@
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B710" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D710" s="5">
         <v>46234</v>
@@ -13250,13 +13259,13 @@
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B711" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D711" s="5">
         <v>46258</v>
@@ -13264,13 +13273,13 @@
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B712" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D712" s="5">
         <v>46285</v>
@@ -13278,13 +13287,13 @@
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B713" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="B713" s="2" t="s">
-        <v>791</v>
-      </c>
       <c r="C713" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D713" s="5">
         <v>46150</v>
@@ -13292,13 +13301,13 @@
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B714" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D714" s="5">
         <v>46192</v>
@@ -13306,13 +13315,13 @@
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B715" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B715" s="2" t="s">
-        <v>794</v>
-      </c>
       <c r="C715" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D715" s="5">
         <v>46353</v>
@@ -13320,13 +13329,13 @@
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B716" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D716" s="5">
         <v>46072</v>
@@ -13334,13 +13343,13 @@
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B717" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D717" s="5">
         <v>46116</v>
@@ -13348,7 +13357,7 @@
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B718" s="2" t="s">
         <v>3</v>
@@ -13362,13 +13371,13 @@
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B719" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D719" s="5">
         <v>46385</v>
@@ -13376,13 +13385,13 @@
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B720" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D720" s="5">
         <v>46077</v>
@@ -13390,13 +13399,13 @@
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B721" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D721" s="5">
         <v>46331</v>
@@ -13404,13 +13413,13 @@
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B722" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D722" s="5">
         <v>46131</v>
@@ -13418,13 +13427,13 @@
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B723" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D723" s="5">
         <v>46353</v>
@@ -13432,13 +13441,13 @@
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B724" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D724" s="5">
         <v>46078</v>
@@ -13446,13 +13455,13 @@
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B725" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D725" s="5">
         <v>46387</v>
@@ -13460,13 +13469,13 @@
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B726" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D726" s="5">
         <v>46067</v>
@@ -13474,13 +13483,13 @@
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B727" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D727" s="5">
         <v>46205</v>
@@ -13488,13 +13497,13 @@
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B728" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D728" s="5">
         <v>46142</v>
@@ -13502,13 +13511,13 @@
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B729" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D729" s="5">
         <v>46146</v>
@@ -13516,7 +13525,7 @@
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B730" s="2" t="s">
         <v>4</v>
@@ -13530,13 +13539,13 @@
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B731" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D731" s="5">
         <v>46071</v>
@@ -13544,13 +13553,13 @@
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B732" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D732" s="5">
         <v>46196</v>
@@ -13558,7 +13567,7 @@
     </row>
     <row r="733" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B733" s="2" t="s">
         <v>20</v>
@@ -13572,13 +13581,13 @@
     </row>
     <row r="734" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B734" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D734" s="5">
         <v>46253</v>
@@ -13586,13 +13595,13 @@
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B735" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D735" s="5">
         <v>46099</v>
@@ -13600,13 +13609,13 @@
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B736" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D736" s="5">
         <v>46032</v>
@@ -13614,13 +13623,13 @@
     </row>
     <row r="737" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B737" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D737" s="5">
         <v>46207</v>
@@ -13628,13 +13637,13 @@
     </row>
     <row r="738" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B738" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D738" s="5">
         <v>46329</v>
@@ -13642,13 +13651,13 @@
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B739" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D739" s="5">
         <v>46111</v>
@@ -13656,13 +13665,13 @@
     </row>
     <row r="740" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B740" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D740" s="5">
         <v>46274</v>
@@ -13670,13 +13679,13 @@
     </row>
     <row r="741" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D741" s="5">
         <v>46274</v>
@@ -13684,13 +13693,13 @@
     </row>
     <row r="742" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B742" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D742" s="5">
         <v>46128</v>
@@ -13698,13 +13707,13 @@
     </row>
     <row r="743" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B743" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D743" s="5">
         <v>46362</v>
@@ -13712,13 +13721,13 @@
     </row>
     <row r="744" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B744" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D744" s="5">
         <v>46196</v>
@@ -13726,13 +13735,13 @@
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B745" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D745" s="5">
         <v>46376</v>
@@ -13740,13 +13749,13 @@
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B746" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D746" s="5">
         <v>46228</v>
@@ -13754,13 +13763,13 @@
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B747" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D747" s="5">
         <v>46304</v>
@@ -13768,13 +13777,13 @@
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B748" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D748" s="5">
         <v>46079</v>
@@ -13782,13 +13791,13 @@
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B749" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D749" s="5">
         <v>46081</v>
@@ -13796,13 +13805,13 @@
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B750" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C750" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D750" s="5">
         <v>46306</v>
@@ -13810,13 +13819,13 @@
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B751" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C751" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D751" s="5">
         <v>46309</v>
@@ -13824,13 +13833,13 @@
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B752" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C752" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D752" s="5">
         <v>46023</v>
@@ -13838,13 +13847,13 @@
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B753" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C753" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D753" s="5">
         <v>46187</v>
@@ -13852,13 +13861,13 @@
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B754" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C754" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D754" s="5">
         <v>46052</v>
@@ -13866,13 +13875,13 @@
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B755" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D755" s="5">
         <v>46211</v>
@@ -13880,13 +13889,13 @@
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B756" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D756" s="5">
         <v>46075</v>
@@ -13894,13 +13903,13 @@
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B757" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C757" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D757" s="5">
         <v>46112</v>
@@ -13908,13 +13917,13 @@
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C758" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D758" s="5">
         <v>46361</v>
@@ -13922,13 +13931,13 @@
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D759" s="5">
         <v>46077</v>
@@ -13936,13 +13945,13 @@
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B760" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D760" s="5">
         <v>46264</v>
@@ -13950,13 +13959,13 @@
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D761" s="5">
         <v>46098</v>
@@ -13964,13 +13973,13 @@
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C762" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D762" s="5">
         <v>46044</v>
@@ -13978,13 +13987,13 @@
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B763" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D763" s="5">
         <v>46189</v>
@@ -13992,13 +14001,13 @@
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B764" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D764" s="5">
         <v>46336</v>
@@ -14006,13 +14015,13 @@
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B765" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C765" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D765" s="5">
         <v>46080</v>
@@ -14020,13 +14029,13 @@
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B766" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C766" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D766" s="5">
         <v>46233</v>
@@ -14034,13 +14043,13 @@
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B767" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C767" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D767" s="5">
         <v>46367</v>
@@ -14048,13 +14057,13 @@
     </row>
     <row r="768" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B768" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C768" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D768" s="5">
         <v>46068</v>
@@ -14062,13 +14071,13 @@
     </row>
     <row r="769" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B769" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D769" s="5">
         <v>46210</v>
@@ -14076,13 +14085,13 @@
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B770" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D770" s="5">
         <v>46248</v>
@@ -14090,13 +14099,13 @@
     </row>
     <row r="771" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B771" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D771" s="5">
         <v>46317</v>
@@ -14104,13 +14113,13 @@
     </row>
     <row r="772" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B772" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D772" s="5">
         <v>46074</v>
@@ -14118,13 +14127,13 @@
     </row>
     <row r="773" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B773" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D773" s="5">
         <v>46285</v>
@@ -14132,13 +14141,13 @@
     </row>
     <row r="774" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B774" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D774" s="5">
         <v>46220</v>
@@ -14146,13 +14155,13 @@
     </row>
     <row r="775" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D775" s="5">
         <v>46387</v>
@@ -14160,13 +14169,13 @@
     </row>
     <row r="776" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B776" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D776" s="5">
         <v>46162</v>
@@ -14174,13 +14183,13 @@
     </row>
     <row r="777" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D777" s="5">
         <v>46126</v>
@@ -14188,13 +14197,13 @@
     </row>
     <row r="778" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D778" s="5">
         <v>46320</v>
@@ -14202,13 +14211,13 @@
     </row>
     <row r="779" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B779" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D779" s="5">
         <v>46160</v>
@@ -14216,13 +14225,13 @@
     </row>
     <row r="780" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D780" s="5">
         <v>46075</v>
@@ -14230,13 +14239,13 @@
     </row>
     <row r="781" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B781" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D781" s="5">
         <v>46166</v>
@@ -14244,13 +14253,13 @@
     </row>
     <row r="782" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B782" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D782" s="5">
         <v>46325</v>
@@ -14258,13 +14267,13 @@
     </row>
     <row r="783" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B783" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D783" s="5">
         <v>46143</v>
@@ -14272,7 +14281,7 @@
     </row>
     <row r="784" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B784" s="2" t="s">
         <v>9</v>
@@ -14286,7 +14295,7 @@
     </row>
     <row r="785" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>9</v>
@@ -14300,7 +14309,7 @@
     </row>
     <row r="786" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B786" s="2" t="s">
         <v>9</v>
@@ -14314,7 +14323,7 @@
     </row>
     <row r="787" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B787" s="2" t="s">
         <v>9</v>
@@ -14328,7 +14337,7 @@
     </row>
     <row r="788" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B788" s="2" t="s">
         <v>9</v>
@@ -14342,7 +14351,7 @@
     </row>
     <row r="789" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B789" s="2" t="s">
         <v>9</v>
@@ -14356,7 +14365,7 @@
     </row>
     <row r="790" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B790" s="2" t="s">
         <v>9</v>
@@ -14370,7 +14379,7 @@
     </row>
     <row r="791" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B791" s="2" t="s">
         <v>9</v>
@@ -14384,13 +14393,13 @@
     </row>
     <row r="792" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B792" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C792" s="2" t="s">
-        <v>264</v>
+        <v>962</v>
       </c>
       <c r="D792" s="5">
         <v>46174</v>
@@ -14398,7 +14407,7 @@
     </row>
     <row r="793" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B793" s="2" t="s">
         <v>22</v>
@@ -14412,7 +14421,7 @@
     </row>
     <row r="794" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B794" s="2" t="s">
         <v>9</v>
@@ -14426,7 +14435,7 @@
     </row>
     <row r="795" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B795" s="2" t="s">
         <v>20</v>
@@ -14440,7 +14449,7 @@
     </row>
     <row r="796" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B796" s="2" t="s">
         <v>22</v>
@@ -14454,7 +14463,7 @@
     </row>
     <row r="797" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B797" s="2" t="s">
         <v>22</v>
@@ -14468,7 +14477,7 @@
     </row>
     <row r="798" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B798" s="2" t="s">
         <v>9</v>
@@ -14482,13 +14491,13 @@
     </row>
     <row r="799" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B799" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C799" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D799" s="5">
         <v>46300</v>
@@ -14496,13 +14505,13 @@
     </row>
     <row r="800" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B800" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C800" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D800" s="5">
         <v>46103</v>
@@ -14510,7 +14519,7 @@
     </row>
     <row r="801" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B801" s="2" t="s">
         <v>4</v>
@@ -14524,13 +14533,13 @@
     </row>
     <row r="802" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B802" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C802" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D802" s="5">
         <v>46246</v>
@@ -14538,13 +14547,13 @@
     </row>
     <row r="803" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B803" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C803" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D803" s="5">
         <v>46182</v>
@@ -14552,7 +14561,7 @@
     </row>
     <row r="804" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B804" s="2" t="s">
         <v>87</v>
@@ -14566,7 +14575,7 @@
     </row>
     <row r="805" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B805" s="2" t="s">
         <v>20</v>
@@ -14580,7 +14589,7 @@
     </row>
     <row r="806" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B806" s="2" t="s">
         <v>9</v>
@@ -14594,13 +14603,13 @@
     </row>
     <row r="807" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B807" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D807" s="5">
         <v>46157</v>
@@ -14608,7 +14617,7 @@
     </row>
     <row r="808" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B808" s="2" t="s">
         <v>22</v>
@@ -14622,7 +14631,7 @@
     </row>
     <row r="809" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B809" s="2" t="s">
         <v>5</v>
@@ -14636,13 +14645,13 @@
     </row>
     <row r="810" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B810" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C810" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D810" s="5">
         <v>46203</v>
@@ -14650,7 +14659,7 @@
     </row>
     <row r="811" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B811" s="2" t="s">
         <v>22</v>
@@ -14664,7 +14673,7 @@
     </row>
     <row r="812" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B812" s="2" t="s">
         <v>9</v>
@@ -14678,7 +14687,7 @@
     </row>
     <row r="813" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B813" s="2" t="s">
         <v>27</v>
@@ -14692,7 +14701,7 @@
     </row>
     <row r="814" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B814" s="2" t="s">
         <v>22</v>
@@ -14706,13 +14715,13 @@
     </row>
     <row r="815" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B815" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C815" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D815" s="5">
         <v>46350</v>
@@ -14720,7 +14729,7 @@
     </row>
     <row r="816" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B816" s="2" t="s">
         <v>22</v>
@@ -14734,7 +14743,7 @@
     </row>
     <row r="817" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B817" s="2" t="s">
         <v>20</v>
@@ -14748,7 +14757,7 @@
     </row>
     <row r="818" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B818" s="2" t="s">
         <v>20</v>
@@ -14762,7 +14771,7 @@
     </row>
     <row r="819" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B819" s="2" t="s">
         <v>22</v>
@@ -14776,7 +14785,7 @@
     </row>
     <row r="820" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B820" s="2" t="s">
         <v>20</v>
@@ -14790,7 +14799,7 @@
     </row>
     <row r="821" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B821" s="2" t="s">
         <v>27</v>
@@ -14804,10 +14813,10 @@
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C822" s="2" t="s">
         <v>101</v>
@@ -14818,7 +14827,7 @@
     </row>
     <row r="823" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B823" s="2" t="s">
         <v>20</v>
@@ -14832,7 +14841,7 @@
     </row>
     <row r="824" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B824" s="2" t="s">
         <v>22</v>
@@ -14846,13 +14855,13 @@
     </row>
     <row r="825" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B825" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C825" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D825" s="5">
         <v>46240</v>
@@ -14860,7 +14869,7 @@
     </row>
     <row r="826" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B826" s="2" t="s">
         <v>20</v>
@@ -14874,7 +14883,7 @@
     </row>
     <row r="827" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B827" s="2" t="s">
         <v>27</v>
@@ -14888,7 +14897,7 @@
     </row>
     <row r="828" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B828" s="2" t="s">
         <v>20</v>
@@ -14902,7 +14911,7 @@
     </row>
     <row r="829" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B829" s="2" t="s">
         <v>22</v>
@@ -14916,10 +14925,10 @@
     </row>
     <row r="830" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B830" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C830" s="2" t="s">
         <v>101</v>
@@ -14930,7 +14939,7 @@
     </row>
     <row r="831" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B831" s="2" t="s">
         <v>20</v>
@@ -14944,7 +14953,7 @@
     </row>
     <row r="832" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B832" s="2" t="s">
         <v>20</v>
@@ -14958,7 +14967,7 @@
     </row>
     <row r="833" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B833" s="2" t="s">
         <v>48</v>
@@ -14972,7 +14981,7 @@
     </row>
     <row r="834" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B834" s="2" t="s">
         <v>48</v>
@@ -14986,7 +14995,7 @@
     </row>
     <row r="835" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B835" s="2" t="s">
         <v>48</v>
@@ -15000,7 +15009,7 @@
     </row>
     <row r="836" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B836" s="2" t="s">
         <v>48</v>
@@ -15014,7 +15023,7 @@
     </row>
     <row r="837" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B837" s="2" t="s">
         <v>9</v>
@@ -15028,7 +15037,7 @@
     </row>
     <row r="838" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B838" s="2" t="s">
         <v>9</v>
@@ -15042,7 +15051,7 @@
     </row>
     <row r="839" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B839" s="2" t="s">
         <v>9</v>
@@ -15056,7 +15065,7 @@
     </row>
     <row r="840" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B840" s="2" t="s">
         <v>48</v>
@@ -15070,7 +15079,7 @@
     </row>
     <row r="841" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B841" s="2" t="s">
         <v>48</v>
@@ -15084,10 +15093,10 @@
     </row>
     <row r="842" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B842" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C842" s="2" t="s">
         <v>101</v>
@@ -15098,7 +15107,7 @@
     </row>
     <row r="843" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B843" s="2" t="s">
         <v>87</v>
@@ -15112,13 +15121,13 @@
     </row>
     <row r="844" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B844" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C844" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D844" s="5">
         <v>46343</v>
@@ -15126,13 +15135,13 @@
     </row>
     <row r="845" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B845" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C845" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D845" s="5">
         <v>46345</v>
@@ -15140,13 +15149,13 @@
     </row>
     <row r="846" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B846" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C846" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D846" s="5">
         <v>46309</v>
@@ -15154,13 +15163,13 @@
     </row>
     <row r="847" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B847" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C847" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D847" s="5">
         <v>46257</v>
@@ -15168,13 +15177,13 @@
     </row>
     <row r="848" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B848" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C848" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D848" s="5">
         <v>46237</v>
@@ -15182,13 +15191,13 @@
     </row>
     <row r="849" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B849" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C849" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D849" s="5">
         <v>46211</v>
@@ -15196,13 +15205,13 @@
     </row>
     <row r="850" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B850" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C850" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D850" s="5">
         <v>46216</v>
@@ -15210,13 +15219,13 @@
     </row>
     <row r="851" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B851" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C851" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D851" s="5">
         <v>46105</v>
@@ -15224,13 +15233,13 @@
     </row>
     <row r="852" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B852" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C852" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D852" s="5">
         <v>46327</v>
@@ -15238,13 +15247,13 @@
     </row>
     <row r="853" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B853" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C853" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D853" s="5">
         <v>46149</v>
@@ -15252,13 +15261,13 @@
     </row>
     <row r="854" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B854" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C854" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D854" s="5">
         <v>46171</v>
@@ -15266,13 +15275,13 @@
     </row>
     <row r="855" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B855" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C855" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D855" s="5">
         <v>46210</v>
@@ -15280,13 +15289,13 @@
     </row>
     <row r="856" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B856" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C856" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D856" s="5">
         <v>46034</v>
@@ -15294,13 +15303,13 @@
     </row>
     <row r="857" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B857" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C857" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D857" s="5">
         <v>46052</v>
@@ -15308,13 +15317,13 @@
     </row>
     <row r="858" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B858" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C858" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D858" s="5">
         <v>46144</v>
@@ -15322,13 +15331,13 @@
     </row>
     <row r="859" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B859" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C859" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D859" s="5">
         <v>46082</v>
@@ -15336,13 +15345,13 @@
     </row>
     <row r="860" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B860" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C860" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D860" s="5">
         <v>46299</v>
@@ -15350,13 +15359,13 @@
     </row>
     <row r="861" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B861" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C861" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D861" s="5">
         <v>46028</v>
@@ -15364,13 +15373,13 @@
     </row>
     <row r="862" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B862" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C862" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D862" s="5">
         <v>46127</v>
@@ -15378,13 +15387,13 @@
     </row>
     <row r="863" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B863" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C863" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D863" s="5">
         <v>46234</v>
@@ -15392,13 +15401,13 @@
     </row>
     <row r="864" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B864" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C864" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D864" s="5">
         <v>46358</v>
@@ -15406,13 +15415,13 @@
     </row>
     <row r="865" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B865" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C865" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D865" s="5">
         <v>46142</v>
@@ -15420,13 +15429,13 @@
     </row>
     <row r="866" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B866" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D866" s="5">
         <v>46175</v>
@@ -15434,13 +15443,13 @@
     </row>
     <row r="867" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="B867" s="2" t="s">
         <v>946</v>
       </c>
-      <c r="B867" s="2" t="s">
-        <v>947</v>
-      </c>
       <c r="C867" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D867" s="5">
         <v>46106</v>
@@ -15448,13 +15457,13 @@
     </row>
     <row r="868" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B868" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C868" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D868" s="5">
         <v>46282</v>
@@ -15462,13 +15471,13 @@
     </row>
     <row r="869" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B869" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C869" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D869" s="5">
         <v>46282</v>
@@ -15476,13 +15485,13 @@
     </row>
     <row r="870" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B870" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C870" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D870" s="5">
         <v>46103</v>
@@ -15490,13 +15499,13 @@
     </row>
     <row r="871" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B871" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C871" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D871" s="5">
         <v>46334</v>
@@ -15504,13 +15513,13 @@
     </row>
     <row r="872" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B872" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C872" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D872" s="5">
         <v>46127</v>
@@ -15518,13 +15527,13 @@
     </row>
     <row r="873" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B873" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C873" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D873" s="5">
         <v>46315</v>
@@ -15532,13 +15541,13 @@
     </row>
     <row r="874" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B874" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C874" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D874" s="5">
         <v>46264</v>
@@ -15546,13 +15555,13 @@
     </row>
     <row r="875" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B875" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C875" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D875" s="5">
         <v>46191</v>
@@ -15560,13 +15569,13 @@
     </row>
     <row r="876" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B876" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C876" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D876" s="5">
         <v>46334</v>
@@ -15574,13 +15583,13 @@
     </row>
     <row r="877" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B877" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C877" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D877" s="5">
         <v>46358</v>
